--- a/data/trans_dic/P04D$individual-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P04D$individual-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, tiene calefacción individual en su vivienda</t>
+          <t>Población que, al menos, tiene calefacción individual en su vivienda (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,94; 28,52</t>
+          <t>18,57; 28,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>29,42; 41,37</t>
+          <t>29,0; 40,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29,77; 43,01</t>
+          <t>29,99; 42,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,86; 30,28</t>
+          <t>19,64; 29,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>35,31; 47,15</t>
+          <t>34,98; 46,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,14; 36,98</t>
+          <t>27,81; 36,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,5; 27,84</t>
+          <t>20,78; 27,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>33,5; 42,06</t>
+          <t>34,0; 41,79</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>30,48; 38,83</t>
+          <t>30,33; 38,26</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,42; 25,08</t>
+          <t>17,32; 24,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>33,02; 42,08</t>
+          <t>32,99; 41,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,48; 5,42</t>
+          <t>1,41; 5,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,89; 22,76</t>
+          <t>15,68; 22,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>38,87; 47,83</t>
+          <t>38,97; 48,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,96; 4,78</t>
+          <t>1,89; 4,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,46; 22,6</t>
+          <t>17,58; 22,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>37,33; 43,66</t>
+          <t>37,21; 43,63</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,01; 4,4</t>
+          <t>1,97; 4,31</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,86; 26,95</t>
+          <t>17,57; 27,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,53; 19,81</t>
+          <t>11,62; 19,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,69; 19,97</t>
+          <t>11,52; 19,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,75; 23,4</t>
+          <t>14,84; 23,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,24; 20,14</t>
+          <t>12,37; 20,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,71; 16,01</t>
+          <t>9,87; 16,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,65; 23,56</t>
+          <t>17,3; 23,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,95; 18,58</t>
+          <t>13,1; 18,74</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,75; 16,86</t>
+          <t>11,72; 16,78</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>27,6; 38,12</t>
+          <t>27,93; 37,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,89; 34,6</t>
+          <t>24,64; 34,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39,82; 54,7</t>
+          <t>40,24; 54,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,98; 36,56</t>
+          <t>26,82; 36,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,81; 32,28</t>
+          <t>22,04; 32,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,85; 37,22</t>
+          <t>18,29; 37,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,75; 35,68</t>
+          <t>28,86; 35,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25,33; 32,12</t>
+          <t>25,23; 32,2</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>26,09; 42,22</t>
+          <t>25,01; 41,83</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,62; 28,56</t>
+          <t>16,39; 28,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,83; 13,92</t>
+          <t>5,83; 13,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,93</t>
+          <t>0,0; 1,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23,56; 35,79</t>
+          <t>23,79; 36,32</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,39; 12,98</t>
+          <t>5,56; 12,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 4,23</t>
+          <t>0,82; 4,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,52; 29,97</t>
+          <t>21,29; 30,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,42; 11,78</t>
+          <t>6,49; 11,76</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,73</t>
+          <t>0,67; 2,85</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20,4; 31,38</t>
+          <t>20,59; 31,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20,72; 31,29</t>
+          <t>20,16; 31,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11,97; 20,15</t>
+          <t>11,71; 19,56</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19,82; 30,27</t>
+          <t>19,29; 29,83</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>25,93; 36,95</t>
+          <t>26,36; 38,07</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,31; 17,25</t>
+          <t>10,51; 17,89</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,94; 28,75</t>
+          <t>21,52; 29,1</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>24,78; 32,55</t>
+          <t>24,73; 32,65</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12,1; 17,46</t>
+          <t>11,96; 17,42</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>21,52; 28,47</t>
+          <t>21,36; 28,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>21,7; 28,86</t>
+          <t>21,53; 28,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25,08; 34,01</t>
+          <t>25,24; 33,42</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21,25; 28,34</t>
+          <t>21,19; 27,76</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>22,78; 29,92</t>
+          <t>22,73; 29,9</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,07; 31,35</t>
+          <t>9,95; 31,32</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,15; 26,94</t>
+          <t>22,02; 26,96</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>23,1; 28,07</t>
+          <t>23,33; 28,22</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>17,05; 30,67</t>
+          <t>15,38; 30,73</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>44,16; 51,58</t>
+          <t>43,56; 50,95</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>31,21; 38,29</t>
+          <t>31,04; 38,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,12; 68,64</t>
+          <t>5,15; 66,63</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>38,53; 45,63</t>
+          <t>38,86; 46,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>33,36; 40,12</t>
+          <t>33,45; 40,59</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,37; 7,17</t>
+          <t>4,33; 7,34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,05; 47,22</t>
+          <t>42,06; 47,22</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>33,35; 38,0</t>
+          <t>33,21; 38,18</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,37; 50,41</t>
+          <t>5,33; 54,53</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>28,3; 31,41</t>
+          <t>28,11; 31,42</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>26,91; 30,21</t>
+          <t>27,03; 30,17</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17,81; 42,85</t>
+          <t>17,86; 42,2</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26,82; 29,97</t>
+          <t>26,82; 29,74</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>29,27; 32,61</t>
+          <t>29,22; 32,39</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,5; 16,91</t>
+          <t>12,48; 16,79</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,9; 30,17</t>
+          <t>27,88; 30,06</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>28,57; 30,91</t>
+          <t>28,63; 30,88</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>16,37; 30,53</t>
+          <t>16,14; 29,59</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, tiene calefacción individual en su vivienda</t>
+          <t>Población que, al menos, tiene calefacción individual en su vivienda (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>52566; 83545</t>
+          <t>54396; 84126</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>86419; 121542</t>
+          <t>85192; 118287</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>92725; 133953</t>
+          <t>93395; 133729</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>56825; 86644</t>
+          <t>56190; 84985</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>101947; 136131</t>
+          <t>100982; 133357</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>81513; 107095</t>
+          <t>80539; 105781</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>118681; 161211</t>
+          <t>120349; 162014</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>195127; 245003</t>
+          <t>198063; 243388</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>183229; 233389</t>
+          <t>182308; 229950</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>87746; 126299</t>
+          <t>87234; 125348</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>165961; 211492</t>
+          <t>165802; 208709</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7663; 28114</t>
+          <t>7318; 27647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>82898; 118755</t>
+          <t>81791; 119732</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>203320; 250169</t>
+          <t>203822; 251258</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10079; 24615</t>
+          <t>9729; 23194</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>178981; 231672</t>
+          <t>180229; 233282</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>382901; 447841</t>
+          <t>381634; 447470</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20780; 45484</t>
+          <t>20359; 44512</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>57887; 87325</t>
+          <t>56929; 87756</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>36722; 63112</t>
+          <t>37027; 62297</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>36825; 62909</t>
+          <t>36289; 62261</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>50294; 79782</t>
+          <t>50593; 79633</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>41157; 67741</t>
+          <t>41604; 68575</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>33783; 55706</t>
+          <t>34336; 56895</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>117376; 156671</t>
+          <t>115037; 156430</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>84794; 121691</t>
+          <t>85809; 122717</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>77917; 111780</t>
+          <t>77696; 111270</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>102948; 142177</t>
+          <t>104179; 141001</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>92086; 128023</t>
+          <t>91167; 127696</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>124462; 170958</t>
+          <t>125778; 171057</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>104947; 142201</t>
+          <t>104335; 141779</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>88338; 125012</t>
+          <t>85372; 124733</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>84496; 176221</t>
+          <t>86568; 177761</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>219092; 271842</t>
+          <t>219880; 272438</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>191788; 243199</t>
+          <t>191076; 243834</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>205045; 331858</t>
+          <t>196572; 328790</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>35344; 60726</t>
+          <t>34854; 60115</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>12311; 29397</t>
+          <t>12321; 29370</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3452</t>
+          <t>0; 3425</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>51746; 78595</t>
+          <t>52234; 79758</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>11784; 28365</t>
+          <t>12161; 27759</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2361; 10918</t>
+          <t>2115; 11484</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>93021; 129525</t>
+          <t>92009; 129927</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>27600; 50652</t>
+          <t>27894; 50541</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2921; 11930</t>
+          <t>2939; 12478</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>55893; 85963</t>
+          <t>56411; 86740</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>54506; 82320</t>
+          <t>53043; 81805</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>32268; 54329</t>
+          <t>31575; 52742</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>55297; 84481</t>
+          <t>53843; 83230</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>70827; 100910</t>
+          <t>71992; 103970</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26513; 44354</t>
+          <t>27013; 45987</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>115793; 159005</t>
+          <t>119022; 160918</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>132894; 174531</t>
+          <t>132615; 175082</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>63709; 91970</t>
+          <t>62987; 91747</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>142604; 188693</t>
+          <t>141553; 188561</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>142486; 189455</t>
+          <t>141355; 188576</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>155805; 211303</t>
+          <t>156823; 207645</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>147463; 196617</t>
+          <t>147009; 192600</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>157504; 206810</t>
+          <t>157106; 206716</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>76636; 265001</t>
+          <t>84138; 264730</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>300447; 365431</t>
+          <t>298754; 365700</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>311404; 378398</t>
+          <t>314418; 380380</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>250086; 449813</t>
+          <t>225540; 450617</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>342973; 400585</t>
+          <t>338309; 395743</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>242997; 298091</t>
+          <t>241646; 297947</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>47451; 636025</t>
+          <t>47736; 617419</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>317391; 375900</t>
+          <t>320141; 378935</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>275592; 331471</t>
+          <t>276386; 335381</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>31331; 51476</t>
+          <t>31076; 52681</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>672966; 755799</t>
+          <t>673202; 755816</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>535126; 609785</t>
+          <t>532999; 612624</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>88286; 828988</t>
+          <t>87687; 896633</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>967788; 1074169</t>
+          <t>961210; 1074530</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>913455; 1025358</t>
+          <t>917657; 1024029</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>615159; 1480020</t>
+          <t>616833; 1457534</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>953284; 1065229</t>
+          <t>953120; 1056955</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1037651; 1155967</t>
+          <t>1035693; 1148130</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>462986; 626384</t>
+          <t>462330; 621803</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1946023; 2104058</t>
+          <t>1944460; 2096331</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1982149; 2144756</t>
+          <t>1986461; 2142806</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1172093; 2185682</t>
+          <t>1155383; 2117910</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P04D$individual-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P04D$individual-Provincia-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>32,29%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,57; 28,72</t>
+          <t>18,23; 28,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>29,0; 40,27</t>
+          <t>29,17; 40,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29,99; 42,94</t>
+          <t>29,07; 40,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,64; 29,7</t>
+          <t>19,66; 30,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>34,98; 46,19</t>
+          <t>35,36; 46,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,81; 36,52</t>
+          <t>26,34; 34,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,78; 27,98</t>
+          <t>20,23; 27,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>34,0; 41,79</t>
+          <t>33,88; 42,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>30,33; 38,26</t>
+          <t>29,07; 35,93</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,32; 24,89</t>
+          <t>17,1; 24,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>32,99; 41,53</t>
+          <t>33,01; 41,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,41; 5,33</t>
+          <t>1,77; 6,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,68; 22,95</t>
+          <t>15,73; 22,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>38,97; 48,03</t>
+          <t>38,76; 47,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,5</t>
+          <t>1,79; 4,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,58; 22,75</t>
+          <t>17,46; 22,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>37,21; 43,63</t>
+          <t>37,27; 43,61</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,97; 4,31</t>
+          <t>2,1; 4,36</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,98%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,57; 27,08</t>
+          <t>17,84; 27,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,62; 19,56</t>
+          <t>11,33; 19,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,52; 19,76</t>
+          <t>11,92; 20,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,84; 23,35</t>
+          <t>14,42; 23,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,37; 20,39</t>
+          <t>12,41; 20,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,87; 16,35</t>
+          <t>9,83; 16,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,3; 23,52</t>
+          <t>17,61; 23,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,1; 18,74</t>
+          <t>12,79; 18,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,72; 16,78</t>
+          <t>11,65; 16,78</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>39,76%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>27,93; 37,8</t>
+          <t>27,86; 38,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,64; 34,52</t>
+          <t>25,03; 34,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40,24; 54,73</t>
+          <t>36,62; 50,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,82; 36,45</t>
+          <t>27,49; 36,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,04; 32,21</t>
+          <t>22,7; 32,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,29; 37,55</t>
+          <t>32,18; 40,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,86; 35,75</t>
+          <t>28,71; 35,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25,23; 32,2</t>
+          <t>25,45; 31,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25,01; 41,83</t>
+          <t>35,51; 43,92</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,39; 28,27</t>
+          <t>17,07; 28,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,83; 13,9</t>
+          <t>5,72; 13,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,92</t>
+          <t>0,0; 1,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23,79; 36,32</t>
+          <t>23,46; 35,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,56; 12,7</t>
+          <t>5,61; 12,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,82; 4,45</t>
+          <t>1,08; 3,52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,29; 30,06</t>
+          <t>21,68; 30,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,49; 11,76</t>
+          <t>6,44; 12,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,85</t>
+          <t>0,66; 2,12</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,18%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20,59; 31,66</t>
+          <t>20,7; 31,87</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20,16; 31,09</t>
+          <t>20,74; 31,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11,71; 19,56</t>
+          <t>11,33; 19,14</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19,29; 29,83</t>
+          <t>19,67; 30,25</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>26,36; 38,07</t>
+          <t>25,79; 36,97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,51; 17,89</t>
+          <t>9,99; 17,27</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21,52; 29,1</t>
+          <t>21,86; 30,17</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>24,73; 32,65</t>
+          <t>25,09; 32,61</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11,96; 17,42</t>
+          <t>11,5; 16,95</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>28,96%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>21,36; 28,45</t>
+          <t>21,31; 28,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>21,53; 28,72</t>
+          <t>21,57; 28,71</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25,24; 33,42</t>
+          <t>24,99; 33,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21,19; 27,76</t>
+          <t>21,05; 27,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>22,73; 29,9</t>
+          <t>22,74; 29,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,95; 31,32</t>
+          <t>26,39; 32,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,02; 26,96</t>
+          <t>22,14; 26,95</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>23,33; 28,22</t>
+          <t>23,21; 28,56</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>15,38; 30,73</t>
+          <t>26,65; 31,51</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>43,56; 50,95</t>
+          <t>43,79; 51,71</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>31,04; 38,27</t>
+          <t>31,22; 38,4</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,15; 66,63</t>
+          <t>4,04; 7,46</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>38,86; 46,0</t>
+          <t>38,46; 45,75</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>33,45; 40,59</t>
+          <t>33,6; 40,41</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,33; 7,34</t>
+          <t>4,39; 7,13</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,06; 47,22</t>
+          <t>42,38; 47,24</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>33,21; 38,18</t>
+          <t>33,22; 38,1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,33; 54,53</t>
+          <t>4,66; 6,97</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>17,22%</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>28,11; 31,42</t>
+          <t>28,16; 31,38</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>27,03; 30,17</t>
+          <t>26,99; 30,25</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17,86; 42,2</t>
+          <t>16,47; 19,43</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26,82; 29,74</t>
+          <t>26,77; 29,71</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>29,22; 32,39</t>
+          <t>29,4; 32,68</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,48; 16,79</t>
+          <t>15,55; 17,83</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,88; 30,06</t>
+          <t>27,96; 30,2</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>28,63; 30,88</t>
+          <t>28,61; 30,87</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>16,14; 29,59</t>
+          <t>16,35; 18,14</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>112550</t>
+          <t>108844</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93865</t>
+          <t>96155</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>206415</t>
+          <t>204999</t>
         </is>
       </c>
     </row>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>54396; 84126</t>
+          <t>53415; 84869</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>85192; 118287</t>
+          <t>85703; 119973</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>93395; 133729</t>
+          <t>92693; 127522</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>56190; 84985</t>
+          <t>56254; 87470</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>100982; 133357</t>
+          <t>102091; 135509</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>80539; 105781</t>
+          <t>83246; 109939</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>120349; 162014</t>
+          <t>117135; 161389</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>198063; 243388</t>
+          <t>197335; 245022</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>182308; 229950</t>
+          <t>184546; 228104</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14829</t>
+          <t>16976</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15679</t>
+          <t>15507</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>30508</t>
+          <t>32483</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>87234; 125348</t>
+          <t>86093; 124253</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>165802; 208709</t>
+          <t>165882; 210048</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7318; 27647</t>
+          <t>9383; 31990</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>81791; 119732</t>
+          <t>82074; 118033</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>203822; 251258</t>
+          <t>202739; 250061</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9729; 23194</t>
+          <t>9802; 24417</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>180229; 233282</t>
+          <t>179035; 233072</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>381634; 447470</t>
+          <t>382219; 447329</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20359; 44512</t>
+          <t>22648; 46960</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>48027</t>
+          <t>48914</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44396</t>
+          <t>44734</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>92423</t>
+          <t>93648</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>56929; 87756</t>
+          <t>57809; 87489</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>37027; 62297</t>
+          <t>36082; 61926</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>36289; 62261</t>
+          <t>37549; 63185</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>50593; 79633</t>
+          <t>49187; 78838</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>41604; 68575</t>
+          <t>41727; 67833</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>34336; 56895</t>
+          <t>34922; 57439</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>115037; 156430</t>
+          <t>117088; 157072</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>85809; 122717</t>
+          <t>83781; 120261</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>77696; 111270</t>
+          <t>78035; 112411</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>146257</t>
+          <t>162828</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>138232</t>
+          <t>151957</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>284489</t>
+          <t>314784</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>104179; 141001</t>
+          <t>103924; 143298</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>91167; 127696</t>
+          <t>92611; 128149</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>125778; 171057</t>
+          <t>136638; 186931</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>104335; 141779</t>
+          <t>106919; 143222</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>85372; 124733</t>
+          <t>87906; 125552</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>86568; 177761</t>
+          <t>134679; 171481</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>219880; 272438</t>
+          <t>218766; 272156</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>191076; 243834</t>
+          <t>192739; 241889</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>196572; 328790</t>
+          <t>281105; 347671</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>728</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5324</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>5309</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>34854; 60115</t>
+          <t>36298; 60113</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>12321; 29370</t>
+          <t>12091; 29131</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3425</t>
+          <t>0; 3676</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>52234; 79758</t>
+          <t>51527; 77128</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>12161; 27759</t>
+          <t>12267; 27668</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2115; 11484</t>
+          <t>2471; 8050</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>92009; 129927</t>
+          <t>93684; 130807</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>27894; 50541</t>
+          <t>27682; 51896</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2939; 12478</t>
+          <t>2855; 9199</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>41435</t>
+          <t>40562</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>35007</t>
+          <t>35250</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>76442</t>
+          <t>75812</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>56411; 86740</t>
+          <t>56725; 87331</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>53043; 81805</t>
+          <t>54571; 83334</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>31575; 52742</t>
+          <t>30670; 51825</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>53843; 83230</t>
+          <t>54884; 84416</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>71992; 103970</t>
+          <t>70430; 100981</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>27013; 45987</t>
+          <t>26359; 45559</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>119022; 160918</t>
+          <t>120870; 166840</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>132615; 175082</t>
+          <t>134526; 174893</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>62987; 91747</t>
+          <t>61459; 90607</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>182515</t>
+          <t>204319</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>194445</t>
+          <t>224314</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>376960</t>
+          <t>428633</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>141553; 188561</t>
+          <t>141247; 186718</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>141355; 188576</t>
+          <t>141598; 188501</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>156823; 207645</t>
+          <t>178038; 235085</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>147009; 192600</t>
+          <t>146066; 192752</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>157106; 206716</t>
+          <t>157193; 206313</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>84138; 264730</t>
+          <t>202672; 250866</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>298754; 365700</t>
+          <t>300295; 365597</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>314418; 380380</t>
+          <t>312831; 384927</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>225540; 450617</t>
+          <t>394456; 466436</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>283420</t>
+          <t>45020</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>40991</t>
+          <t>47527</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>324411</t>
+          <t>92548</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>338309; 395743</t>
+          <t>340142; 401627</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>241646; 297947</t>
+          <t>243040; 298968</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>47736; 617419</t>
+          <t>32119; 59321</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>320141; 378935</t>
+          <t>316861; 376913</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>276386; 335381</t>
+          <t>277612; 333893</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>31076; 52681</t>
+          <t>36535; 59278</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>673202; 755816</t>
+          <t>678335; 756166</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>532999; 612624</t>
+          <t>533098; 611421</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>87687; 896633</t>
+          <t>75827; 113351</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>829707</t>
+          <t>628191</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>567939</t>
+          <t>620026</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1397646</t>
+          <t>1248217</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>961210; 1074530</t>
+          <t>962831; 1073187</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>917657; 1024029</t>
+          <t>916057; 1026634</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>616833; 1457534</t>
+          <t>580015; 684328</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>953120; 1056955</t>
+          <t>951445; 1055961</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1035693; 1148130</t>
+          <t>1041940; 1158477</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>462330; 621803</t>
+          <t>579647; 664506</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1944460; 2096331</t>
+          <t>1950028; 2105918</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1986461; 2142806</t>
+          <t>1984874; 2142094</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1155383; 2117910</t>
+          <t>1185152; 1315414</t>
         </is>
       </c>
     </row>
